--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-befund.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-befund.xlsx
@@ -1299,7 +1299,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
